--- a/src/attributions/attributions_ig_traj_63.xlsx
+++ b/src/attributions/attributions_ig_traj_63.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2401135718327312</v>
+        <v>0.05380656385636928</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0140801560651949</v>
+        <v>-0.02139823761105743</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08771111286612951</v>
+        <v>-0.01868366248445272</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2906157891536152</v>
+        <v>0.1278781253806107</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0358600814397469</v>
+        <v>-0.06037005245205495</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1932773041918927</v>
+        <v>-0.03000859227516564</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1034339462766803</v>
+        <v>0.01991073305065785</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,88 +1065,88 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01733637254209362</v>
+        <v>-0.03098810985872901</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.02245833149949888</v>
+        <v>-0.007979436596747484</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.09325170396931458</v>
+        <v>-0.03668762908330347</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1024054121559777</v>
+        <v>-0.05243496975883052</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.01447407317991855</v>
+        <v>0.01956318029578975</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05819421552473314</v>
+        <v>0.02862374524250613</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06145869996344114</v>
+        <v>0.0003752406696478738</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.04523293167539676</v>
+        <v>-0.001426715514340385</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4652930052654325</v>
+        <v>0.1564334786314305</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2059223397221895</v>
+        <v>-0.03034881746174236</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.1085833661937733</v>
+        <v>-0.005889861145971374</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.01497336419801861</v>
+        <v>-0.0125043144095998</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,118 +1173,118 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.0584831599896254</v>
+        <v>-0.02157452367959296</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.08281310754167936</v>
+        <v>-0.02515340913403407</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.008569524986570478</v>
+        <v>0.01932786715050654</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2217526125318197</v>
+        <v>0.06217552148150382</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.06167726038931939</v>
+        <v>0.0237546624872509</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.263408830484369</v>
+        <v>0.0789200719865506</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.04562560671262003</v>
+        <v>-0.02407100780931731</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.00655716325980756</v>
+        <v>-0.02281840442157813</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1035779858496723</v>
+        <v>-0.03629085887368274</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.00772876860713151</v>
+        <v>0.01477672764119727</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.07893466034238669</v>
+        <v>0.01918415120746841</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.0178335450325998</v>
+        <v>-0.03618342289610574</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.07884842517949775</v>
+        <v>0.009299305285042974</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,67 +1293,67 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.008131724451474979</v>
+        <v>0.01652395550440972</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1078577198193598</v>
+        <v>-0.03707892237935195</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.01472427226528075</v>
+        <v>0.007754473987182757</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.05569553906492418</v>
+        <v>0.02105856475467793</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1515221385556389</v>
+        <v>-0.07268954175025055</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08823705833602717</v>
+        <v>-0.003640289512432711</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.03900878186288913</v>
+        <v>0.0007447448303006248</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.03483814335940599</v>
+        <v>-0.01491485195287007</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.06723529231841541</v>
+        <v>0.01992273286225981</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.02245010770205791</v>
+        <v>0.02138340655754953</v>
       </c>
       <c r="DW2" t="n">
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1913342440829243</v>
+        <v>-0.02588450699890033</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0001449379106833827</v>
+        <v>-0.02515239860900435</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.02941720684711801</v>
+        <v>0.003409274553592907</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.05857863851749904</v>
+        <v>-0.02277901843543845</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.03436525696013095</v>
+        <v>-0.005156275274103611</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,70 +1425,70 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.116672240125666</v>
+        <v>0.01362082946059988</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.06152038553364275</v>
+        <v>-0.01450475774656364</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03974710345427596</v>
+        <v>0.01863068317384468</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.05942128069912744</v>
+        <v>0.02493307197460365</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.113552479540678</v>
+        <v>-0.04886003043606304</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.009310381767495627</v>
+        <v>0.006693270378896748</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.05332452789403964</v>
+        <v>0.01928143033406151</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.01455440470229459</v>
+        <v>0.03569807410282105</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,10 +1497,10 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.04825999083153915</v>
+        <v>-0.004514116507706927</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.007260091596141512</v>
+        <v>0.03204805873137394</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.004100733793769637</v>
+        <v>-0.01094676829681697</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,25 +1524,25 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.009366827224002013</v>
+        <v>0.009964663130331534</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.04629353680999698</v>
+        <v>0.006220679385014413</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.08793757615938069</v>
+        <v>-0.02571183359009154</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.04646745385941742</v>
+        <v>-0.01020954467167298</v>
       </c>
     </row>
     <row r="3">
@@ -2706,25 +2706,25 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1440077652532893</v>
+        <v>0.003097167775715803</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02428023240476643</v>
+        <v>-0.001456265054656667</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1331424991379911</v>
+        <v>-0.002041385499197949</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,25 +2736,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1459464855510647</v>
+        <v>0.007945942303453121</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03307468297338797</v>
+        <v>-0.002097209992705584</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1727874212409578</v>
+        <v>-0.00575831778978702</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,88 +2763,88 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08698254305910248</v>
+        <v>-0.0001238670562630102</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2028755195369007</v>
+        <v>-0.002743779815444217</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.09537501979532592</v>
+        <v>0.0003739440471631364</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1240645042575592</v>
+        <v>-0.003384566463346457</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.06226149280185612</v>
+        <v>-0.004885299974133893</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.03372613911676436</v>
+        <v>2.173233009696543e-05</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0224031094689459</v>
+        <v>-0.0002746019900882593</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02671554120032863</v>
+        <v>-0.0009403060590911054</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.04054227664899581</v>
+        <v>0.000314918882833005</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2460300342743855</v>
+        <v>0.00946242837645583</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,13 +2853,13 @@
         <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1239233227207288</v>
+        <v>-2.103374084601251e-06</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2359326872462183</v>
+        <v>-0.0006942493998243068</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2868,10 +2868,10 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03723999267516932</v>
+        <v>-0.001325296665808329</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02879200940769539</v>
+        <v>-0.001222231072322838</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.02207133957087884</v>
+        <v>-0.0005494764083542993</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003668135513173867</v>
+        <v>0.002162728365857083</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1642468218780935</v>
+        <v>0.005217371890440937</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.06378653480600423</v>
+        <v>-0.0005229206684961431</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.08357207867505934</v>
+        <v>0.004854869485462657</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1121724913537736</v>
+        <v>-0.0001963920963045091</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.1309565648877117</v>
+        <v>-0.0007792724340966446</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.06573784909116479</v>
+        <v>-0.001220549988900148</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.03652005283769238</v>
+        <v>0.001130280083228348</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.04655129376029526</v>
+        <v>0.0008168785685038658</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2976,25 +2976,25 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.08874584423317432</v>
+        <v>-0.00235528361103365</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.04475011223343484</v>
+        <v>-0.0002043856836396226</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.05681079310065514</v>
+        <v>-0.001342111060916781</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3003,25 +3003,25 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.04312654954719555</v>
+        <v>-0.001293175310002143</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01886235696774003</v>
+        <v>0.0004966366055078165</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.05170339495334903</v>
+        <v>0.001345824360083586</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.08079965866433585</v>
+        <v>-0.002193359329216767</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,25 +3042,25 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02859969612113416</v>
+        <v>-0.002455034230561798</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.03570079121181379</v>
+        <v>0.0005229466423995396</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.0313927698070006</v>
+        <v>0.0005261454468419455</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,40 +3069,40 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02502553889022186</v>
+        <v>0.001146315965370105</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.02895414078188051</v>
+        <v>0.002016809756168815</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1521595156749506</v>
+        <v>-0.001762314845113926</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
         <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01294114316924572</v>
+        <v>-0.0007023245727779288</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.03636857835846618</v>
+        <v>0.002804307689960961</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,25 +3114,25 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01949009336769904</v>
+        <v>-0.0007417447567674503</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03637315793677363</v>
+        <v>0.0002935355024863635</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.06779392023346693</v>
+        <v>-2.873123620355375e-06</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,49 +3141,49 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03252691588664201</v>
+        <v>-0.0005057113866818113</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.007470194176614067</v>
+        <v>-0.0005824271917137839</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.01536898583690515</v>
+        <v>0.0008537589741259868</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.05772843283018302</v>
+        <v>-0.001881833688894854</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.03324695225949686</v>
+        <v>0.0001395485956502962</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.04180013341169467</v>
+        <v>0.0009388786652703153</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,52 +3192,52 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.06054256505824417</v>
+        <v>0.00150625031376803</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.003098563373677188</v>
+        <v>-0.001374124876052752</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.04747016840239422</v>
+        <v>-0.001517025469723861</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.006583305623180558</v>
+        <v>-0.0001179698486955953</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.006729325520747679</v>
+        <v>0.0001919710221751497</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.02852434377951387</v>
+        <v>0.002128140214585099</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
@@ -3246,10 +3246,10 @@
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.06935768878410095</v>
+        <v>-0.0009191097805992688</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3258,13 +3258,13 @@
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1878893057222895</v>
+        <v>0.002639624718533279</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4012151070762464</v>
+        <v>0.3316922023687073</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2500254357833316</v>
+        <v>-0.3433984148122177</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004620544062256122</v>
+        <v>0.01702478710656414</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3714021916284084</v>
+        <v>0.4709798143752039</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2757348668193681</v>
+        <v>-0.4174109663597753</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03110510778172687</v>
+        <v>-0.03373015370001264</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1647534420636644</v>
+        <v>0.2015812284739133</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01396249026984723</v>
+        <v>-0.03652822414800693</v>
       </c>
       <c r="W7" t="n">
-        <v>0.112929239280519</v>
+        <v>-0.0373627117799263</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,73 +3925,73 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1162625381823473</v>
+        <v>-0.1485259176466416</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0103669386833786</v>
+        <v>-0.2136444336831453</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.05483323845895928</v>
+        <v>-0.1734584371357658</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01009719916482289</v>
+        <v>0.2415761085417428</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1150964591259905</v>
+        <v>-0.09764455212884766</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06498742919083007</v>
+        <v>0.1614048761507767</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4525197456669849</v>
+        <v>0.4444373604608048</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.06051138525847439</v>
+        <v>-0.2683588300083229</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2018818049314169</v>
+        <v>-0.201079862803434</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02392361239138066</v>
+        <v>-0.0715120092885055</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.06587560817505626</v>
+        <v>-0.1039793632842669</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0823736148074678</v>
+        <v>-0.0669129628713255</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4033,79 +4033,79 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04673151351423487</v>
+        <v>-0.1084259637891031</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06285087849358593</v>
+        <v>0.1046005247828332</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1888118223943561</v>
+        <v>-0.06390076885661872</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2132711911004352</v>
+        <v>0.4819012664726764</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.008748527857643082</v>
+        <v>-0.1944924843134493</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1206695107982376</v>
+        <v>-0.02916733385493043</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1153068015113571</v>
+        <v>-0.1383705516345006</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.03269127673352415</v>
+        <v>0.2035686107054845</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0314668931880487</v>
+        <v>-0.03911650505767834</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.01210954277261306</v>
+        <v>-0.08158617859617825</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1667911443458907</v>
+        <v>0.4704928238120329</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1434122867429266</v>
+        <v>0.2605127261777965</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.110411261742363</v>
+        <v>-0.1368516358167627</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.06493866782070368</v>
+        <v>0.2096389573843368</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02469010390088113</v>
+        <v>-0.02055815066044493</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.138431843996184</v>
+        <v>-0.2452711042220114</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001306593664047617</v>
+        <v>0.08715941869251918</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.007851418423987525</v>
+        <v>-0.122768948180248</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.008658618814457304</v>
+        <v>-0.03877294420305495</v>
       </c>
       <c r="DP7" t="n">
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.0923709987143566</v>
+        <v>0.06383848671701627</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.08382257045268177</v>
+        <v>0.02307759816627142</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,103 +4225,103 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0677822353051627</v>
+        <v>-0.02814143752275747</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.009459266464950388</v>
+        <v>-0.1160767301712432</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.009314979453201788</v>
+        <v>-0.1244560207851242</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1109378697295043</v>
+        <v>-0.08385462517677643</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05062521302125283</v>
+        <v>0.1621709442616099</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.07599665650671514</v>
+        <v>0.01487922275354207</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1100759152765054</v>
+        <v>-0.1587894643482217</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.07378588942990699</v>
+        <v>0.1171141875165182</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.007993774820147027</v>
+        <v>-0.017715878901956</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1109018811560479</v>
+        <v>-0.1694005656060373</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0376200841724867</v>
+        <v>0.2362279001092543</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03053802286455222</v>
+        <v>-0.03783292230337525</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,19 +4330,19 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.003698716984742162</v>
+        <v>-0.1435894322610044</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.08573415672512238</v>
+        <v>0.171087776703657</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.003669769504550308</v>
+        <v>0.07085420436935722</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4351,61 +4351,61 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.004835285423681538</v>
+        <v>-0.02592757086567964</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.03473738534119326</v>
+        <v>0.0280733610775418</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.00147146627324495</v>
+        <v>0.03711794595131841</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.004188769615223711</v>
+        <v>-0.2316223786069728</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.08975365576585276</v>
+        <v>0.1257067052043891</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1843888942319332</v>
+        <v>0.5557061685255583</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01035268142252774</v>
+        <v>-0.04415622403367135</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1130635019506334</v>
+        <v>-0.1697773615438159</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,73 +4443,73 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1724416454317237</v>
+        <v>0.882519400622474</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.004712821799062347</v>
+        <v>-0.1770199830870772</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1736088953322788</v>
+        <v>-0.2596219985015056</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02525293073835106</v>
+        <v>0.2872399379984683</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.03343056325913253</v>
+        <v>-0.1210330115981939</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006934381646439346</v>
+        <v>-0.04304875309324708</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03255306744038865</v>
+        <v>0.08296852228920154</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03247834701995961</v>
+        <v>-0.5009633551590154</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.004169833665025097</v>
+        <v>-0.2291591740816912</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -4521,22 +4521,22 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01436635619759897</v>
+        <v>0.2919295188136481</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02176303930459076</v>
+        <v>0.08748134219225218</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04671130425378683</v>
+        <v>-0.1373211154230201</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.154572105861065</v>
+        <v>1.100666383111363</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
@@ -4560,13 +4560,13 @@
         <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.026796372292423</v>
+        <v>-0.160339217433475</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1027683089854655</v>
+        <v>-0.4077435494697844</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>-0</v>
@@ -4578,73 +4578,73 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04886783711921587</v>
+        <v>-0.0997032914360472</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01455703194100047</v>
+        <v>-0.1585934520002224</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.02209174618624625</v>
+        <v>-0.02043794000802302</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.06077290085055233</v>
+        <v>0.04495404221596588</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01922945975424771</v>
+        <v>0.1089615414627494</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.02386322016819088</v>
+        <v>-0.08599297163539531</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.08071604220985115</v>
+        <v>0.7446051461595051</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.00392564826097323</v>
+        <v>-0.06520263103998335</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03557486459726789</v>
+        <v>-0.225174137749464</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,61 +4659,61 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.04738255203162089</v>
+        <v>-0.297469541480059</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.00678787038130974</v>
+        <v>0.05694243958071595</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04157704703941907</v>
+        <v>0.1383469276996382</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01734350962227129</v>
+        <v>-0.6052900974339316</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.004507933646563978</v>
+        <v>0.3815240659008179</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02986705334992569</v>
+        <v>0.330811618546022</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03755265707511901</v>
+        <v>-0.2771805376803889</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.009495492208805956</v>
+        <v>0.02156738426942795</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04390890180099744</v>
+        <v>0.129471041126581</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,61 +4740,61 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.04827645715200654</v>
+        <v>-0.09100621826639449</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04553606452035922</v>
+        <v>-0.3911221462610978</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0.0005709888500983823</v>
+        <v>0.06254336952633748</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02768542669527649</v>
+        <v>-0.1479562173856072</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01793098152705943</v>
+        <v>0.1045689080904764</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.006136131499585512</v>
+        <v>0.02460701706348029</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02602654337975719</v>
+        <v>0.03163599465911219</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,10 +4803,10 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01559854786248026</v>
+        <v>0.08743270786096007</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.02429204209142738</v>
+        <v>-0.1539486174337723</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4821,22 +4821,22 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.03509545485357162</v>
+        <v>-0.06187355290067468</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.004759078330112402</v>
+        <v>-0.07724375275107744</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0223200528587739</v>
+        <v>0.007539587889992295</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4845,22 +4845,22 @@
         <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01625126943052205</v>
+        <v>-0.1134117426812161</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01421779566298767</v>
+        <v>-0.1119356428944068</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.03728454709639911</v>
+        <v>0.0518974913087813</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
@@ -4875,34 +4875,34 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03828918257760519</v>
+        <v>-0.3121441736571258</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.004110158226891386</v>
+        <v>0.0005638502182395694</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04606891141728292</v>
+        <v>0.1202243239834452</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.00347502173349128</v>
+        <v>-0.3374127325282611</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,37 +4911,37 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03036790433530568</v>
+        <v>0.1253973389892484</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03165058579639515</v>
+        <v>0.1430477197304972</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.003049792514626135</v>
+        <v>-0.06435805195049667</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001399593966380657</v>
+        <v>0.01887848374312946</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02545874353269183</v>
+        <v>0.08229834862303619</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,13 +4950,13 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01337573803783087</v>
+        <v>-0.1482547146400885</v>
       </c>
       <c r="GA8" t="n">
         <v>-0</v>
@@ -4968,13 +4968,13 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.03738998028871125</v>
+        <v>-0.05219786837692082</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -5551,19 +5551,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6078701952894319</v>
+        <v>0.01224338274668843</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.172572331029094</v>
+        <v>-0.005072091058058831</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4965415675857391</v>
+        <v>-0.004036169941319397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4904977040652538</v>
+        <v>0.01985004463188498</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3783579955210251</v>
+        <v>-0.01269886650118721</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,16 +5599,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.8975589193964825</v>
+        <v>-0.01149552438080669</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3420464681530597</v>
+        <v>0.008416706511176625</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,16 +5617,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3236732728674572</v>
+        <v>-0.008748312339547325</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1303151367828247</v>
+        <v>-0.003968734145741091</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
@@ -5635,16 +5635,16 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.32567828964991</v>
+        <v>-0.006964599708681816</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1837643376971874</v>
+        <v>-0.01120830542958517</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,34 +5653,34 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.3327918413422926</v>
+        <v>0.003179696480666992</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1164157726222113</v>
+        <v>0.006306422357205546</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01359613169252122</v>
+        <v>0.0003986531187444138</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.2098640936365915</v>
+        <v>-0.0003219648310595454</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.107888776290674</v>
+        <v>0.02142868172697414</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,43 +5698,43 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.5306029113564124</v>
+        <v>-0.002017919532312288</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.03387385831362077</v>
+        <v>-0.004870993219732883</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02952494138925956</v>
+        <v>-0.004557977440430464</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2820067352458726</v>
+        <v>-0.008266409660777138</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.2103286592948193</v>
+        <v>-0.0003754473932459784</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5666232543696172</v>
+        <v>0.006243759284148082</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,16 +5752,16 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.7924562450246911</v>
+        <v>0.01176138450445596</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.317022127312517</v>
+        <v>0.005653461527751757</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,43 +5770,43 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.5210961570401721</v>
+        <v>0.01840700334535404</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2634195110104856</v>
+        <v>-0.002386393349621525</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.04358652072521354</v>
+        <v>-0.00766416529254924</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1928316719244588</v>
+        <v>-0.003071830497645919</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.002164782265844448</v>
+        <v>0.002481496916800054</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,16 +5815,16 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.2122567845266711</v>
+        <v>0.002576901429052099</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.5045682987193382</v>
+        <v>-0.005201479354514889</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,34 +5833,34 @@
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.593762181675045</v>
+        <v>0.009018116195380512</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.187645311495247</v>
+        <v>0.003426358909006521</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1467247843441021</v>
+        <v>-0.002995731287247185</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.02421457739306713</v>
+        <v>0.002320451762944678</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,52 +5869,52 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.1020165884305498</v>
+        <v>0.003934930401164028</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.7596149185476655</v>
+        <v>-0.003526900036339055</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07832762518933215</v>
+        <v>0.002317617311594481</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.02948457643928555</v>
+        <v>0.001065443947891446</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1828147387699959</v>
+        <v>-0.005161334667935976</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.1009869919091235</v>
+        <v>-0.001950595110709202</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1502824836433378</v>
+        <v>0.000725652504509476</v>
       </c>
       <c r="DV10" t="n">
         <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.05632226269940947</v>
+        <v>0.004687737917772207</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,34 +5941,34 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.08192716756796248</v>
+        <v>-0.005477432987963211</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.1956743503495845</v>
+        <v>-0.007538374528483586</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.09046348072323508</v>
+        <v>0.00382224989862273</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04133886443840597</v>
+        <v>-0.001670706814698843</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,16 +5977,16 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.2286773631142533</v>
+        <v>-0.0008504154718483802</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.07481974021395711</v>
+        <v>-0.001031123363740878</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,34 +5995,34 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1275739469495836</v>
+        <v>-0.003264902719483893</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.003015855104209422</v>
+        <v>0.00352224142650056</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1348301633158986</v>
+        <v>-0.003134771576547557</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.03285928768169188</v>
+        <v>0.0002740463005736542</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,43 +6031,43 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.1979208491394169</v>
+        <v>0.003763834828325387</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.06956283905458385</v>
+        <v>0.000558363555146991</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.1602363269900171</v>
+        <v>0.006299507944262052</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.09242504819473479</v>
+        <v>-0.002789246205843011</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0149176754047686</v>
+        <v>-0.0003984265638757936</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,34 +6076,34 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04546035860726795</v>
+        <v>0.001417937109441725</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.1998680074407093</v>
+        <v>0.00111058024942641</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.3816011206660188</v>
+        <v>-0.005789629234023153</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>0</v>
@@ -6112,60 +6112,60 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.3647736013559778</v>
+        <v>-0.001687651076194873</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.2707214091768073</v>
+        <v>-0.2280451319232874</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5074774441376526</v>
+        <v>0.2974479377764468</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1896615930458511</v>
+        <v>-0.1100290564688962</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1850455462795859</v>
+        <v>-0.1366283491041968</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4258968431891907</v>
+        <v>0.4597715096377182</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4199979349971851</v>
+        <v>-0.1321391596351159</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,19 +6174,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02007418512087081</v>
+        <v>0.06906496042080297</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3261962235502707</v>
+        <v>0.09314700856822256</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2059310835227113</v>
+        <v>0.02086228722895385</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,79 +6195,79 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.03333497543854756</v>
+        <v>-0.1302013080590768</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1909841665608231</v>
+        <v>-0.1154979587657493</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.09432434638311359</v>
+        <v>-0.1650006963904578</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1110062986680288</v>
+        <v>-0.004330501583865894</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2212128488170539</v>
+        <v>0.1810900668356741</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.02597974588566637</v>
+        <v>-0.09940759723245843</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2147975569604381</v>
+        <v>0.01314604514557689</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.6519339249936688</v>
+        <v>0.3677957645271256</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3417118347580521</v>
+        <v>-0.1335101554627793</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6282,25 +6282,25 @@
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.1613228502988767</v>
+        <v>-0.1905682294460188</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.05311064749029159</v>
+        <v>-0.03041817815384696</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.3313621053354832</v>
+        <v>-0.1160195592706757</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.08516725212609745</v>
+        <v>0.04960840141871947</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1122232160193179</v>
+        <v>0.2266629166910699</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.3378521760191397</v>
+        <v>0.1123257967928675</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,49 +6336,49 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.1245711042218914</v>
+        <v>0.09646451446625942</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4029487526928349</v>
+        <v>0.4148814463768595</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.07096805813991476</v>
+        <v>-0.02112288448653808</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0428826136330856</v>
+        <v>0.07800250011863141</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1127444265766923</v>
+        <v>-0.1317587349736997</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01122326441703616</v>
+        <v>0.01988581145431439</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
@@ -6390,46 +6390,46 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.2905302299634419</v>
+        <v>-0.07932387902165211</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.127518989143199</v>
+        <v>-0.28895799477898</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.3153763828125312</v>
+        <v>0.07935350700234331</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01925191319370592</v>
+        <v>0.05078920775941732</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1249607959644102</v>
+        <v>-0.1303776939167449</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01043623181318552</v>
+        <v>-0.001776021033099996</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6444,37 +6444,37 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2764567570474281</v>
+        <v>0.04384371982462675</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.4454087305763272</v>
+        <v>-0.3128971363763727</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07611924096050851</v>
+        <v>-0.006398910249083785</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.1492523341683466</v>
+        <v>-0.02264245729409601</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.1880649043661372</v>
+        <v>-0.04969849426432577</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
@@ -6483,67 +6483,67 @@
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.05666994190352299</v>
+        <v>0.01120883768791641</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.04869654111746502</v>
+        <v>0.1418376818971271</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1297667886481208</v>
+        <v>0.1465561331207629</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.1220629937281391</v>
+        <v>-0.06073247774455274</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.07104764345710869</v>
+        <v>-0.0004986213103845153</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1720342465805183</v>
+        <v>0.002808615023279274</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.005631028614871183</v>
+        <v>-0.04062483091005365</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.03856160436148627</v>
+        <v>-0.03692055223950472</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.09110731076979021</v>
+        <v>-0.09860691393994657</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.03345904693938878</v>
+        <v>-0.1013356118050572</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6573,16 +6573,16 @@
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.04102282689885545</v>
+        <v>0.06110295346801548</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1148610157129268</v>
+        <v>-0.1705803020177284</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,37 +6591,37 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.05339437890875692</v>
+        <v>-0.01917588350544118</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.176731585559352</v>
+        <v>0.02604355403491446</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.07201295218070231</v>
+        <v>-0.01605696909893276</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.09409508568705237</v>
+        <v>0.03157672834729487</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
@@ -6633,37 +6633,37 @@
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.004602285086210482</v>
+        <v>-0.04823297095334447</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03073929229167813</v>
+        <v>0.01467173174181488</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01631544618180665</v>
+        <v>0.06198314105887124</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.06657447807152221</v>
+        <v>0.05537309672713202</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.173102891702359</v>
+        <v>-0.110890104562536</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6672,10 +6672,10 @@
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,34 +6692,34 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5824102386383335</v>
+        <v>0.04577427628195496</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2881052849798458</v>
+        <v>-0.1173056345956543</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3044310111558047</v>
+        <v>-0.1201932067275987</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4193871797555048</v>
+        <v>0.1000418480068531</v>
       </c>
       <c r="L12" t="n">
         <v>-0</v>
@@ -6728,13 +6728,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3012031448909107</v>
+        <v>-0.1212867351325235</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2625274625917272</v>
+        <v>-0.1651710982976905</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,22 +6746,22 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2077718204277583</v>
+        <v>0.06264040175926731</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
         <v>-0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2256666892402747</v>
+        <v>-0.02562888353575822</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.03059047530289946</v>
+        <v>0.04163050230619393</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6773,34 +6773,34 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2424100632008525</v>
+        <v>-0.1062893364481472</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>-0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.06468693113392178</v>
+        <v>-0.1769573569014994</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.02889067137988132</v>
+        <v>0.03091856307803804</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07632833437670559</v>
+        <v>0.1315753250777712</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,16 +6809,16 @@
         <v>-0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0001151986740524891</v>
+        <v>0.02861394295518719</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08095123652481216</v>
+        <v>0.02707805666871441</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6311367939521345</v>
+        <v>0.2681999236148685</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,40 +6836,40 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.009197745691937631</v>
+        <v>0.02692208069470199</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.1842342980375409</v>
+        <v>0.005792561999689446</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1162555256108723</v>
+        <v>-0.1426864688307457</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1205080762383365</v>
+        <v>-0.1388586739165434</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.1275358199575496</v>
+        <v>-0.04370213202084882</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1093627432842006</v>
+        <v>-0.02070966846663409</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.2292352911318397</v>
+        <v>0.07952779677879827</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.02101660101861928</v>
+        <v>0.08232074004187775</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,34 +6908,34 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2676600407406005</v>
+        <v>0.2123869428920647</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.01189587731086874</v>
+        <v>-0.01421284282056693</v>
       </c>
       <c r="BZ12" t="n">
         <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.07597566641323297</v>
+        <v>0.001581666908184082</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.155632955620349</v>
+        <v>-0.01883256526149786</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,13 +6944,13 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.05498488373518511</v>
+        <v>0.04126791184568709</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.07308536761529867</v>
+        <v>0.01772870519627779</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.2355077368817647</v>
+        <v>-0.09800055190362345</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
         <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1802521855658216</v>
+        <v>0.07042194577344485</v>
       </c>
       <c r="CR12" t="n">
         <v>0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.003461734148436727</v>
+        <v>-0.1135197282466137</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1224972407053651</v>
+        <v>-0.02257786276983655</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.04764818309290721</v>
+        <v>0.04132087637921677</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.06413322552574288</v>
+        <v>0.03026674533237273</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7013,106 +7013,106 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.3744950078600637</v>
+        <v>-0.05174280315596268</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04368829130686323</v>
+        <v>-0.004048292129582145</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.1037096425742668</v>
+        <v>-0.04937564664931383</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.08792483675022678</v>
+        <v>0.00351430620915761</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.04059864972759172</v>
+        <v>0.08781644617012355</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.02496240735886893</v>
+        <v>0.04579774670229503</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1476524374914841</v>
+        <v>0.01981130167881692</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.08021595195992738</v>
+        <v>-0.05525489733710454</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.003966523419875172</v>
+        <v>-0.004796038812680837</v>
       </c>
       <c r="ED12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.04034402614480631</v>
+        <v>-0.01696821224856216</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.08734917776379049</v>
+        <v>0.009567336319397256</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0896346889911684</v>
+        <v>-0.02363308416089829</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,10 +7121,10 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.0513434457536235</v>
+        <v>-0.008423257293803268</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
@@ -7133,25 +7133,25 @@
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04503177562002618</v>
+        <v>-0.01159125571498344</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.009343821042865717</v>
+        <v>-0.05535508149814568</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1328875008728389</v>
+        <v>-0.0170271881094655</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.04707532121686669</v>
+        <v>0.025060173183405</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.06437341307497001</v>
+        <v>0.01498539830078935</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,25 +7175,25 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.04482719156449076</v>
+        <v>-0.03552781269476903</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1171308848122798</v>
+        <v>-0.02905703038523588</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.06166479026267591</v>
+        <v>-0.02428976117390043</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7205,7 +7205,7 @@
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01025211845264527</v>
+        <v>-0.01874899242619821</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01272672503161605</v>
+        <v>-0.008084641145960445</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.04287225277633444</v>
+        <v>0.06911196127436546</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.1170014863837318</v>
+        <v>-0.07161170209051752</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7247,13 +7247,13 @@
         <v>-0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0.01611447726116331</v>
+        <v>0.04735034930536002</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9037999349607546</v>
+        <v>1.336831692974303</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2705469294746717</v>
+        <v>-0.7573103551035478</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5021443778788824</v>
+        <v>-0.2662224792361656</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6468046292151415</v>
+        <v>1.745002573827162</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3037985855491954</v>
+        <v>-0.8886520169988904</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.4744861877901685</v>
+        <v>-0.2744896913029863</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2906729625255864</v>
+        <v>0.3408521887817031</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
@@ -7324,88 +7324,88 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04069169043464379</v>
+        <v>-0.226859307995171</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.09488756153507856</v>
+        <v>-0.2438562859850627</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3372909464536809</v>
+        <v>0.1580317055935871</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.08985694617909631</v>
+        <v>-0.4481144634920387</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.0109412132129853</v>
+        <v>-0.01186866773581409</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1595608387608476</v>
+        <v>0.7306995326867771</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01444501788700834</v>
+        <v>0.3573388118985667</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.0331552472268203</v>
+        <v>-0.01624566574953489</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.8726769546376818</v>
+        <v>2.040561115516308</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.09345030283205286</v>
+        <v>-0.3091324904566454</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.2948946468178634</v>
+        <v>0.03559018532743895</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1155923320879802</v>
+        <v>-0.3748060088241279</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.246610868676664</v>
+        <v>-0.5439536400526539</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7441,70 +7441,70 @@
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.2015268540657818</v>
+        <v>-0.1056058499999746</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.086833185018836</v>
+        <v>0.1184792099004499</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.3713101732684627</v>
+        <v>0.3391186034641103</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0.008970142855151284</v>
+        <v>0.1984991145266752</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.515801096137763</v>
+        <v>1.336194310991227</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.06772297468711064</v>
+        <v>-0.3125075523839794</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.1122891668095904</v>
+        <v>-0.244703995649724</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.2115656499335515</v>
+        <v>-0.6476193457334231</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,34 +7513,34 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01685207636372874</v>
+        <v>0.1693774763082512</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.1635097107038635</v>
+        <v>0.1014493130587797</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.2699571702306918</v>
+        <v>-1.231753248879312</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.2555261266590999</v>
+        <v>0.2702212822206232</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
@@ -7552,40 +7552,40 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.06080644945558242</v>
+        <v>0.004400790748088353</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1785768120426576</v>
+        <v>-0.6048486798318833</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.02600878339154837</v>
+        <v>0.1177506967491532</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.1244044312286271</v>
+        <v>0.1364427277150819</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.4841100155989574</v>
+        <v>-0.4258470924694125</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,7 +7594,7 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1102107805640723</v>
+        <v>-0.01452758659022454</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02305855043652213</v>
+        <v>-0.1407273143396851</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.1062092454104429</v>
+        <v>-0.3099980314867922</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0006145773122293303</v>
+        <v>0.1354862856260338</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,16 +7630,16 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.02749722196058799</v>
+        <v>-0.2824798464608926</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1734068731259362</v>
+        <v>0.5235735874988374</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
@@ -7648,64 +7648,64 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.07525587744372637</v>
+        <v>-0.1825443012314646</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01696296981994286</v>
+        <v>0.3315426490515375</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01837495161129804</v>
+        <v>-0.2459422955892925</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.05101559662607188</v>
+        <v>-0.04532705930611567</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.2208160800479363</v>
+        <v>0.05819167795778246</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1324716509960639</v>
+        <v>-0.3766340109285966</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0165383932825558</v>
+        <v>0.06168786321782523</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.02730382403833688</v>
+        <v>0.1466773068307942</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.2085058711970986</v>
+        <v>-0.7208247791513942</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,100 +7729,100 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.006586434498219426</v>
+        <v>0.1098430019692849</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.1146027077093686</v>
+        <v>0.1481632666880188</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.09918682736472832</v>
+        <v>-0.2286890543129673</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.08080144780507997</v>
+        <v>-0.05933295118266538</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.1267432322124226</v>
+        <v>-0.1825348951379014</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01531709982175753</v>
+        <v>-0.04357036728888653</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.008706671164391099</v>
+        <v>0.07947156079938178</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.03238005456393921</v>
+        <v>-0.06946816958399603</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.2296912627052839</v>
+        <v>-0.3569549367220692</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.04124979428553942</v>
+        <v>0.1176314049884899</v>
       </c>
     </row>
     <row r="14">
@@ -8396,55 +8396,55 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2627926690483666</v>
+        <v>0.6612612271652867</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0810630324891288</v>
+        <v>-0.152831644350516</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1150086910086987</v>
+        <v>-0.5618028206829104</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1992899565628653</v>
+        <v>1.03623578871445</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.04479323194428617</v>
+        <v>-0.1150180350110984</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1576198425833947</v>
+        <v>-0.5422027414524785</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -8453,46 +8453,46 @@
         <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05761226744951054</v>
+        <v>0.217677944204262</v>
       </c>
       <c r="U15" t="n">
-        <v>0.003552895063040842</v>
+        <v>0.1380348277591445</v>
       </c>
       <c r="V15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0008928479117895961</v>
+        <v>0.1432112656554329</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.08603865067054153</v>
+        <v>-0.04434655857785907</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003377954953735742</v>
+        <v>-0.3323977761708916</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.018985285255503</v>
+        <v>-0.1751423526711287</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8504,46 +8504,46 @@
         <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.07234086192318898</v>
+        <v>0.4342051690282698</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.005407077656541557</v>
+        <v>0.04287464538964331</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.02195398602327197</v>
+        <v>0.2686701459219937</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2218761240401053</v>
+        <v>0.9659726295383732</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.05962537974334123</v>
+        <v>0.3055226942811474</v>
       </c>
       <c r="AW15" t="n">
         <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.01191836970848002</v>
+        <v>0.02364629603238114</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -8552,34 +8552,34 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.04930879736987483</v>
+        <v>-0.4394375170891364</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.0385287175569714</v>
+        <v>-0.3088858329168435</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1236258029346373</v>
+        <v>-0.6444002491419889</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,25 +8588,25 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0457895767964064</v>
+        <v>0.08360574295486693</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0.02329819406020149</v>
+        <v>-0.03517327474880293</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.05626802631266279</v>
+        <v>0.1581733301583107</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
@@ -8615,52 +8615,52 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.11747219850488</v>
+        <v>0.8172455536889013</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0.05870696976031666</v>
+        <v>0.1484067036965901</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.007734387552162937</v>
+        <v>0.02001241500819133</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.04803854213134497</v>
+        <v>-0.3668184104155121</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.005109172799418304</v>
+        <v>0.06046687985568501</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.02287529153687776</v>
+        <v>0.1437316065015072</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
@@ -8669,16 +8669,16 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.03490296434830534</v>
+        <v>-0.5903426807211609</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0.005482993538754898</v>
+        <v>0.01469266214299888</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.02062565338317831</v>
+        <v>0.2102302701940447</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8693,19 +8693,19 @@
         <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.03495673270788737</v>
+        <v>-0.3337333738720927</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.002047486234418454</v>
+        <v>0.06738732481709384</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.01200909671627374</v>
+        <v>0.08505738282833662</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8720,19 +8720,19 @@
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.03572616650165913</v>
+        <v>-0.2274937588040356</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.003815109636900963</v>
+        <v>-0.01782525271285477</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.01744499205115463</v>
+        <v>0.03474993698441704</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8744,25 +8744,25 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.0109075793123518</v>
+        <v>-0.1725673122535996</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.001656555506474232</v>
+        <v>-0.104448866099063</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01472167294385269</v>
+        <v>0.2172528478796119</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
@@ -8771,130 +8771,130 @@
         <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.02456818331696473</v>
+        <v>0.4773378872224712</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0.006251669250832904</v>
+        <v>0.08265521171100478</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.001644115847112622</v>
+        <v>-0.3161514522156618</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.01221869326204337</v>
+        <v>-0.1203063932880252</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.004672829279139489</v>
+        <v>-0.06459913469466026</v>
       </c>
       <c r="EI15" t="n">
         <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.04477459866944411</v>
+        <v>0.02779603784608419</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.02027044964127923</v>
+        <v>-0.2403137381578687</v>
       </c>
       <c r="EQ15" t="n">
-        <v>-0.03806107625354927</v>
+        <v>-0.09713418393448905</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.04117208731068238</v>
+        <v>-0.02380437453948299</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.0422605338977448</v>
+        <v>-0.3770962716540165</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.002851375621828333</v>
+        <v>0.04637994598816119</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.02506514579102377</v>
+        <v>0.09176087084165639</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.03794473051473302</v>
+        <v>0.09806495618650085</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0.02061064125384824</v>
+        <v>-0.3019571260614058</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.05740852923746303</v>
+        <v>-0.2570452289347578</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8903,52 +8903,52 @@
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>6.168610604863043e-07</v>
+        <v>0.001963591664565551</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.01352632230284474</v>
+        <v>0.0356998077829328</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.003782219217187453</v>
+        <v>0.04388525430443792</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.01033529071965261</v>
+        <v>-0.299827883134329</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0196689105599196</v>
+        <v>-0.1640749567124895</v>
       </c>
       <c r="GB15" t="n">
         <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
         <v>-0</v>
@@ -8957,7 +8957,7 @@
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
@@ -8968,16 +8968,16 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.297470215612082</v>
+        <v>0.1251897512976105</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.141499551606581</v>
+        <v>-0.0695316859240183</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -8989,40 +8989,40 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.04307612443706872</v>
+        <v>-0.03519158061276972</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1854598829423522</v>
+        <v>0.2000774821039784</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1762701381778839</v>
+        <v>-0.08759552049105472</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.0497255576618784</v>
+        <v>-0.04044138152087354</v>
       </c>
       <c r="S16" t="n">
         <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06065463929443161</v>
+        <v>0.01332240537047331</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,52 +9031,52 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02363991892377217</v>
+        <v>-0.05297644601293584</v>
       </c>
       <c r="X16" t="n">
         <v>-0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.01136929942739121</v>
+        <v>0.002928862679040326</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1202870731692265</v>
+        <v>-0.03517838736594392</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02684103343875652</v>
+        <v>-0.0512273554918207</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01524382942083989</v>
+        <v>-0.003480336930259162</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.07046616443408694</v>
+        <v>0.03228069315092639</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,52 +9085,52 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01157978629039267</v>
+        <v>-0.02751340075449659</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.02957691428101343</v>
+        <v>0.005231928330982232</v>
       </c>
       <c r="AT16" t="n">
         <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2758374818369653</v>
+        <v>0.1694776123980236</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.01238158796472995</v>
+        <v>-0.06166407797462565</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0164738024872832</v>
+        <v>-0.00119253569236757</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.02033456302605653</v>
+        <v>-0.01774403586629072</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,79 +9139,79 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1616179810256886</v>
+        <v>-0.04418268269213677</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0.03617301983232012</v>
+        <v>-0.01711015298486292</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.04737269705555809</v>
+        <v>0.04762224799775443</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0710090463573283</v>
+        <v>0.05532975290909288</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0.001777304005786001</v>
+        <v>0.02741650967832151</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1638090427412578</v>
+        <v>0.1082312288373216</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.004189200710487808</v>
+        <v>-0.05231689825589864</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.01225416859509788</v>
+        <v>-0.009954377333161879</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.04605111501521316</v>
+        <v>-0.03408125728067991</v>
       </c>
       <c r="CF16" t="n">
         <v>-0</v>
@@ -9220,7 +9220,7 @@
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.01637927723758153</v>
+        <v>0.02456635897339923</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
@@ -9232,13 +9232,13 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.007835504145980259</v>
+        <v>0.01727913050245355</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.05231441506726874</v>
+        <v>-0.08402077330982195</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,10 +9247,10 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.01318569635005671</v>
+        <v>0.03356967980868846</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9259,22 +9259,22 @@
         <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0.0302879783077322</v>
+        <v>-0.001052934866171483</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.03181137870341041</v>
+        <v>-0.03200711646266635</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.008147577655955357</v>
+        <v>0.01208057347079904</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
@@ -9286,13 +9286,13 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.01604591199356699</v>
+        <v>0.013310043719757</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.04162916339886686</v>
+        <v>-0.01168128591230096</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
@@ -9301,7 +9301,7 @@
         <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06001134729624377</v>
+        <v>-0.02687800441206846</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
@@ -9313,121 +9313,121 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0.02782535442670992</v>
+        <v>-0.01592501899092947</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.007507242409552972</v>
+        <v>-0.01925020032841455</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.00842086631126978</v>
+        <v>0.01296229085812923</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0.02980456516823454</v>
+        <v>-0.005944759341989828</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.02746859530258368</v>
+        <v>0.04062936268264829</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.03394020224867211</v>
+        <v>-0.006920041869103738</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0.01248358363337077</v>
+        <v>0.01799076330138336</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01406357739598546</v>
+        <v>-0.006665147823503722</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.04111404855240584</v>
+        <v>-0.002485984738687758</v>
       </c>
       <c r="EK16" t="n">
         <v>-0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.03031050489531523</v>
+        <v>0.02151077397848781</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.03780106309024736</v>
+        <v>0.002003287941415903</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.006788016252255897</v>
+        <v>-0.01801727662692135</v>
       </c>
       <c r="ET16" t="n">
         <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0.03043479484609412</v>
+        <v>-0.008330448100776764</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.04306000313452459</v>
+        <v>-0.03978706512475016</v>
       </c>
       <c r="EZ16" t="n">
         <v>-0</v>
@@ -9436,52 +9436,52 @@
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.005689327377190536</v>
+        <v>0.006807691092466968</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.006485631657300266</v>
+        <v>0.01663744161248402</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.03116581675731043</v>
+        <v>-0.02172594792620902</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.03114854560961591</v>
+        <v>0.04129480314285219</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0007418673012406755</v>
+        <v>-0.001488114184253701</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.0002875939119196692</v>
+        <v>-0.0002231771910878537</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,7 +9490,7 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0004393127297132685</v>
+        <v>0.001121318337228423</v>
       </c>
       <c r="FU16" t="n">
         <v>0</v>
@@ -9499,16 +9499,16 @@
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.00603933191697211</v>
+        <v>0.01806043453968263</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.04115484978034142</v>
+        <v>-0.02896371504748402</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
@@ -9517,19 +9517,19 @@
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.002420069112950001</v>
+        <v>0.003585409099614746</v>
       </c>
     </row>
   </sheetData>
